--- a/ig/DM-MARS-2026/CodeSystem-v2-0488.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-v2-0488.xlsx
@@ -115,7 +115,7 @@
     <t>Value Set (all codes)</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0488|2.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0488|3.0.0</t>
   </si>
   <si>
     <t>Hierarchy</t>

--- a/ig/DM-MARS-2026/CodeSystem-v2-0488.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-v2-0488.xlsx
@@ -115,7 +115,7 @@
     <t>Value Set (all codes)</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0488|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0488|2.9</t>
   </si>
   <si>
     <t>Hierarchy</t>
